--- a/AfterToken/Configs/GameConfig/Datas/building.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/building.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,41 @@
           <t>unlockLevel</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>footprintX</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>footprintZ</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>maxCountPerPlayerLevel</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>maxCountUpgradeLevel</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>maxCountSlotBaseCost</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>maxCountSlotCostGrow</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +604,41 @@
           <t>int</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -646,6 +716,41 @@
           <t>解锁等级</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>占地格数X(1m格)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>占地格数Z(1m格)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>数量上限-基础值(默认1)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>数量上限-玩家每升1级+N(默认0)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>数量上限-升级解锁:同类建筑每有1座达到该等级上限+1,0=不启用(默认解锁方式)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>数量上限-购买栏位基础金币价,0=不可购买</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>数量上限-栏位涨价:每购1个价格+N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
@@ -701,6 +806,27 @@
       </c>
       <c r="O4" t="n">
         <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>500</v>
+      </c>
+      <c r="V4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -758,6 +884,27 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>500</v>
+      </c>
+      <c r="V5" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -814,6 +961,27 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>800</v>
+      </c>
+      <c r="V6" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -859,6 +1027,27 @@
       </c>
       <c r="O7" t="n">
         <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>100</v>
+      </c>
+      <c r="V7" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
